--- a/data/sars/pacific/tables/Pacific_2020_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2020_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67370CCC-5803-3440-9AD2-92997791833E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651E4FBF-30E7-2540-BA8D-975FA2635E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="34760" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="138">
   <si>
     <t>California Sea Lion</t>
   </si>
@@ -382,9 +382,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>≥4.8</t>
   </si>
   <si>
@@ -407,6 +404,36 @@
   </si>
   <si>
     <t>species</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>ommited from table</t>
+  </si>
+  <si>
+    <t>≥ 0.4</t>
+  </si>
+  <si>
+    <t>Oʻahu / 4 Islands Region</t>
+  </si>
+  <si>
+    <t>Kaua’i and Niʻihau</t>
+  </si>
+  <si>
+    <t>≥ 1.0</t>
+  </si>
+  <si>
+    <t>Hawai’i Island</t>
   </si>
 </sst>
 </file>
@@ -417,7 +444,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -432,6 +459,12 @@
     <font>
       <sz val="11"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +492,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -508,6 +541,7 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,7 +846,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:Q88"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="40.19921875" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.3984375" style="2" bestFit="1" customWidth="1"/>
@@ -828,13 +862,13 @@
     <col min="11" max="11" width="13.19921875" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="8.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.3984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="40.19921875" style="2"/>
+    <col min="15" max="16" width="12.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="40.19921875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>107</v>
@@ -875,11 +909,17 @@
       <c r="N1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="O1" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -926,7 +966,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -973,7 +1013,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -1016,7 +1056,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -1059,7 +1099,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
@@ -1102,7 +1142,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1145,7 +1185,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -1192,7 +1232,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
@@ -1239,9 +1279,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>7</v>
@@ -1286,9 +1326,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>77</v>
@@ -1312,7 +1352,7 @@
         <v>4.8</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>41</v>
@@ -1332,8 +1372,11 @@
       <c r="O11" s="2">
         <v>2020</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P11" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -1380,7 +1423,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -1427,7 +1470,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -1474,7 +1517,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
@@ -1521,7 +1564,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -1568,7 +1611,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>22</v>
       </c>
@@ -1615,7 +1658,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
         <v>34</v>
       </c>
@@ -1662,7 +1705,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
         <v>36</v>
       </c>
@@ -1709,7 +1752,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
@@ -1756,7 +1799,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>39</v>
       </c>
@@ -1803,7 +1846,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
@@ -1850,7 +1893,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
@@ -1897,7 +1940,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
@@ -1944,7 +1987,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>47</v>
       </c>
@@ -1991,7 +2034,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
@@ -2038,7 +2081,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
         <v>51</v>
       </c>
@@ -2085,12 +2128,12 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C28" s="5">
         <v>73</v>
@@ -2131,8 +2174,11 @@
       <c r="O28" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P28" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>53</v>
       </c>
@@ -2179,7 +2225,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
         <v>54</v>
       </c>
@@ -2226,7 +2272,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
         <v>55</v>
       </c>
@@ -2273,7 +2319,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
         <v>56</v>
       </c>
@@ -2320,7 +2366,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
         <v>58</v>
       </c>
@@ -2367,7 +2413,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
         <v>59</v>
       </c>
@@ -2414,7 +2460,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
         <v>60</v>
       </c>
@@ -2461,7 +2507,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
         <v>61</v>
       </c>
@@ -2507,8 +2553,11 @@
       <c r="O36" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P36" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>61</v>
       </c>
@@ -2554,8 +2603,11 @@
       <c r="O37" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P37" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
         <v>64</v>
       </c>
@@ -2602,7 +2654,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
         <v>67</v>
       </c>
@@ -2649,7 +2701,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>101</v>
       </c>
@@ -2675,10 +2727,10 @@
         <v>81</v>
       </c>
       <c r="I40" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>20</v>
@@ -2695,8 +2747,11 @@
       <c r="O40" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P40" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
         <v>69</v>
       </c>
@@ -2743,7 +2798,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
         <v>71</v>
       </c>
@@ -2790,7 +2845,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
         <v>73</v>
       </c>
@@ -2837,7 +2892,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
         <v>75</v>
       </c>
@@ -2883,8 +2938,11 @@
       <c r="O44" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P44" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
         <v>75</v>
       </c>
@@ -2931,7 +2989,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
@@ -2977,8 +3035,11 @@
       <c r="O46" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P46" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
         <v>39</v>
       </c>
@@ -3024,8 +3085,11 @@
       <c r="O47" s="13">
         <v>2017</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P47" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
         <v>39</v>
       </c>
@@ -3072,7 +3136,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
@@ -3119,7 +3183,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
         <v>39</v>
       </c>
@@ -3166,7 +3230,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
@@ -3213,7 +3277,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
         <v>83</v>
       </c>
@@ -3259,8 +3323,11 @@
       <c r="O52" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="P52" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>83</v>
       </c>
@@ -3303,7 +3370,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>83</v>
       </c>
@@ -3346,7 +3413,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>83</v>
       </c>
@@ -3389,7 +3456,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>85</v>
       </c>
@@ -3434,7 +3501,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>85</v>
       </c>
@@ -3479,7 +3546,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>85</v>
       </c>
@@ -3522,7 +3589,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>85</v>
       </c>
@@ -3565,7 +3632,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A60" s="5" t="s">
         <v>44</v>
       </c>
@@ -3611,8 +3678,11 @@
       <c r="O60" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P60" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A61" s="5" t="s">
         <v>88</v>
       </c>
@@ -3658,8 +3728,11 @@
       <c r="O61" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P61" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="5" t="s">
         <v>89</v>
       </c>
@@ -3705,8 +3778,11 @@
       <c r="O62" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P62" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="5" t="s">
         <v>89</v>
       </c>
@@ -3752,8 +3828,11 @@
       <c r="O63" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P63" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="5" t="s">
         <v>92</v>
       </c>
@@ -3799,8 +3878,11 @@
       <c r="O64" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P64" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="5" t="s">
         <v>93</v>
       </c>
@@ -3846,8 +3928,11 @@
       <c r="O65" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P65" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="5" t="s">
         <v>93</v>
       </c>
@@ -3893,8 +3978,11 @@
       <c r="O66" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+      <c r="P66" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
         <v>93</v>
       </c>
@@ -3937,12 +4025,12 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A68" s="5" t="s">
         <v>93</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C68" s="5">
         <v>167</v>
@@ -3983,8 +4071,11 @@
       <c r="O68" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P68" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
         <v>93</v>
       </c>
@@ -4031,7 +4122,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A70" s="5" t="s">
         <v>51</v>
       </c>
@@ -4077,8 +4168,11 @@
       <c r="O70" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P70" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A71" s="5" t="s">
         <v>96</v>
       </c>
@@ -4124,8 +4218,11 @@
       <c r="O71" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P71" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A72" s="5" t="s">
         <v>97</v>
       </c>
@@ -4171,8 +4268,11 @@
       <c r="O72" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P72" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
         <v>98</v>
       </c>
@@ -4218,8 +4318,11 @@
       <c r="O73" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P73" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
         <v>56</v>
       </c>
@@ -4265,8 +4368,11 @@
       <c r="O74" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P74" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A75" s="5" t="s">
         <v>99</v>
       </c>
@@ -4312,8 +4418,11 @@
       <c r="O75" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P75" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A76" s="5" t="s">
         <v>59</v>
       </c>
@@ -4359,8 +4468,11 @@
       <c r="O76" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P76" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A77" s="5" t="s">
         <v>60</v>
       </c>
@@ -4406,8 +4518,11 @@
       <c r="O77" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P77" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
         <v>67</v>
       </c>
@@ -4452,7 +4567,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A79" s="5" t="s">
         <v>101</v>
       </c>
@@ -4498,8 +4613,11 @@
       <c r="O79" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P79" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" ht="16" x14ac:dyDescent="0.15">
       <c r="A80" s="5" t="s">
         <v>73</v>
       </c>
@@ -4545,8 +4663,11 @@
       <c r="O80" s="13">
         <v>2020</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P80" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
         <v>69</v>
       </c>
@@ -4591,7 +4712,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A82" s="5" t="s">
         <v>71</v>
       </c>
@@ -4637,8 +4758,11 @@
       <c r="O82" s="5">
         <v>2020</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+      <c r="P82" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
         <v>64</v>
       </c>
@@ -4685,7 +4809,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
         <v>102</v>
       </c>
@@ -4732,7 +4856,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="85" spans="1:15" ht="16" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="16" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
         <v>102</v>
       </c>
@@ -4777,6 +4901,156 @@
       </c>
       <c r="O85" s="8">
         <v>2018</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" ht="16" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F86" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="G86" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L86" s="3">
+        <v>1998</v>
+      </c>
+      <c r="M86" s="3">
+        <v>2002</v>
+      </c>
+      <c r="N86" s="8">
+        <v>2007</v>
+      </c>
+      <c r="O86" s="8">
+        <v>2018</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="16" x14ac:dyDescent="0.15">
+      <c r="A87" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F87" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="G87" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L87" s="3">
+        <v>1995</v>
+      </c>
+      <c r="M87" s="3">
+        <v>1998</v>
+      </c>
+      <c r="N87" s="8">
+        <v>2005</v>
+      </c>
+      <c r="O87" s="8">
+        <v>2018</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="16" x14ac:dyDescent="0.15">
+      <c r="A88" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C88" s="3">
+        <v>665</v>
+      </c>
+      <c r="D88" s="3">
+        <v>0.09</v>
+      </c>
+      <c r="E88" s="6">
+        <v>617</v>
+      </c>
+      <c r="F88" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="G88" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H88" s="8">
+        <v>6.2</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K88" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L88" s="3">
+        <v>2010</v>
+      </c>
+      <c r="M88" s="3">
+        <v>2011</v>
+      </c>
+      <c r="N88" s="8">
+        <v>2012</v>
+      </c>
+      <c r="O88" s="8">
+        <v>2018</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
